--- a/FinanceDataMigration/src/main/resources/migration-templates/EXPENSE_BILL.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/EXPENSE_BILL.xlsx
@@ -455,12 +455,12 @@
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font/>
@@ -516,11 +516,11 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -529,7 +529,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -537,22 +537,22 @@
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -561,31 +561,31 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -593,51 +593,51 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -1201,27 +1201,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.25"/>
-    <col customWidth="1" min="2" max="2" width="30"/>
-    <col customWidth="1" min="3" max="3" width="20.5"/>
-    <col customWidth="1" min="4" max="4" width="15.5"/>
-    <col customWidth="1" min="5" max="5" width="15.75"/>
-    <col customWidth="1" min="6" max="8" width="9.140625"/>
-    <col customWidth="1" min="9" max="9" width="22.129999999999999"/>
-    <col customWidth="1" min="10" max="10" width="9.140625"/>
-    <col customWidth="1" min="11" max="11" width="24.129999999999999"/>
-    <col customWidth="1" min="12" max="12" width="14.5"/>
-    <col customWidth="1" min="13" max="13" width="27.629999999999999"/>
-    <col customWidth="1" min="14" max="14" width="16.129999999999999"/>
-    <col customWidth="1" min="15" max="15" width="21.5"/>
-    <col customWidth="1" min="16" max="16" width="12.880000000000001"/>
-    <col customWidth="1" min="17" max="17" width="12.25"/>
-    <col customWidth="1" min="18" max="18" width="21.879999999999999"/>
-    <col customWidth="1" min="19" max="19" width="16"/>
-    <col customWidth="1" min="20" max="20" width="18.629999999999999"/>
-    <col customWidth="1" min="21" max="21" width="13"/>
-    <col customWidth="1" min="22" max="22" width="24.629999999999999"/>
-    <col customWidth="1" min="23" max="23" width="13.25"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="4.23046875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="30.61328125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="24.90234375"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="14.7109375"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="15.3828125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="8.7109375"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="13.28125"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="21.76171875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="21.953125"/>
+    <col bestFit="1" customWidth="1" min="10" max="10" width="13.953125"/>
+    <col bestFit="1" customWidth="1" min="11" max="11" width="29.57421875"/>
+    <col bestFit="1" customWidth="1" min="12" max="12" width="14.04296875"/>
+    <col bestFit="1" customWidth="1" min="13" max="13" width="33.8515625"/>
+    <col bestFit="1" customWidth="1" min="14" max="14" width="19.57421875"/>
+    <col bestFit="1" customWidth="1" min="15" max="15" width="25.953125"/>
+    <col bestFit="1" customWidth="1" min="16" max="16" width="15.3828125"/>
+    <col bestFit="1" customWidth="1" min="17" max="17" width="14.7109375"/>
+    <col bestFit="1" customWidth="1" min="18" max="18" width="26.5234375"/>
+    <col bestFit="1" customWidth="1" min="19" max="19" width="19.3828125"/>
+    <col bestFit="1" customWidth="1" min="20" max="20" width="22.421875"/>
+    <col bestFit="1" customWidth="1" min="21" max="21" width="15.57421875"/>
+    <col bestFit="1" customWidth="1" min="22" max="22" width="30.04296875"/>
+    <col bestFit="1" customWidth="1" min="23" max="23" width="15.953125"/>
     <col customWidth="1" min="24" max="26" width="9.140625"/>
   </cols>
   <sheetData>
@@ -29322,28 +29324,8 @@
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:W3"/>
   </mergeCells>
-  <dataValidations count="7" disablePrompts="0">
-    <dataValidation sqref="E5:E997" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$B$2:$B$40</formula1>
-    </dataValidation>
-    <dataValidation sqref="H5:H997" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="B5:B997" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="D5:D998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Fund!$C$4:$C$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M997" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$J$2:$J$23</formula1>
-    </dataValidation>
-    <dataValidation sqref="F5:F998" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Scheme!$C$4:$C$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="L5:L997" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$I$2:$I$15</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
